--- a/iphone-dates.xlsx
+++ b/iphone-dates.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10112"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10308"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bogdanratiu/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bogdanratiu/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85CBECBA-5BF2-FE42-A369-97ED31C2AD88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C5FB6F-2CCA-B34B-B450-9504D3601F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>iPhone XS, XS Max</t>
   </si>
@@ -108,6 +108,9 @@
   </si>
   <si>
     <t>Iphone 16e</t>
+  </si>
+  <si>
+    <t>Iphone 17</t>
   </si>
 </sst>
 </file>
@@ -487,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="48.5" bestFit="1" customWidth="1"/>
@@ -679,6 +682,14 @@
         <v>45716</v>
       </c>
     </row>
+    <row r="24" spans="1:2" ht="31" x14ac:dyDescent="0.35">
+      <c r="A24" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="6">
+        <v>46284</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B22">
     <sortCondition ref="B2:B22"/>

--- a/iphone-dates.xlsx
+++ b/iphone-dates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bogdanratiu/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C5FB6F-2CCA-B34B-B450-9504D3601F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B41EA69-C0AB-5B44-B91E-457F09A86A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -687,7 +687,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="6">
-        <v>46284</v>
+        <v>45919</v>
       </c>
     </row>
   </sheetData>
